--- a/public/templates/true_false_template.xlsx
+++ b/public/templates/true_false_template.xlsx
@@ -397,19 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="80.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:K6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,6 +415,24 @@
       <c r="E1" t="str">
         <v>Correct Answer</v>
       </c>
+      <c r="F1" t="str">
+        <v>Difficulty</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Company Name</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Exam Name</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Exam Year</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Section Name</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -444,6 +450,24 @@
       <c r="E2" t="str">
         <v>false</v>
       </c>
+      <c r="F2" t="str">
+        <v>easy</v>
+      </c>
+      <c r="G2" t="str">
+        <v>programming</v>
+      </c>
+      <c r="H2" t="str">
+        <v>tcs</v>
+      </c>
+      <c r="I2" t="str">
+        <v>nqt</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K2" t="str">
+        <v>coding</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -461,6 +485,24 @@
       <c r="E3" t="str">
         <v>true</v>
       </c>
+      <c r="F3" t="str">
+        <v>medium</v>
+      </c>
+      <c r="G3" t="str">
+        <v>logical</v>
+      </c>
+      <c r="H3" t="str">
+        <v>infosys, wipro</v>
+      </c>
+      <c r="I3" t="str">
+        <v>infytq, wiprotest</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2025, 2026</v>
+      </c>
+      <c r="K3" t="str">
+        <v>coding, technical</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -478,6 +520,24 @@
       <c r="E4" t="str">
         <v>true</v>
       </c>
+      <c r="F4" t="str">
+        <v>hard</v>
+      </c>
+      <c r="G4" t="str">
+        <v>math</v>
+      </c>
+      <c r="H4" t="str">
+        <v>cognizant</v>
+      </c>
+      <c r="I4" t="str">
+        <v>genC</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026</v>
+      </c>
+      <c r="K4" t="str">
+        <v>logical</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -495,6 +555,24 @@
       <c r="E5" t="str">
         <v>false</v>
       </c>
+      <c r="F5" t="str">
+        <v>medium</v>
+      </c>
+      <c r="G5" t="str">
+        <v>fundamentals</v>
+      </c>
+      <c r="H5" t="str">
+        <v>amazon</v>
+      </c>
+      <c r="I5" t="str">
+        <v>aws-cert</v>
+      </c>
+      <c r="J5" t="str">
+        <v>2024</v>
+      </c>
+      <c r="K5" t="str">
+        <v>verbal</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -512,10 +590,28 @@
       <c r="E6" t="str">
         <v>false</v>
       </c>
+      <c r="F6" t="str">
+        <v>easy</v>
+      </c>
+      <c r="G6" t="str">
+        <v>science</v>
+      </c>
+      <c r="H6" t="str">
+        <v>google, microsoft</v>
+      </c>
+      <c r="I6" t="str">
+        <v>g-kickstart, ms-codility</v>
+      </c>
+      <c r="J6" t="str">
+        <v>2024, 2025</v>
+      </c>
+      <c r="K6" t="str">
+        <v>algorithms, technical</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
 </file>